--- a/results/greedy_baseline_comparison.xlsx
+++ b/results/greedy_baseline_comparison.xlsx
@@ -5,17 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mmarathe/Documents/GitHub/CATS-CaliforniaTestSystem/results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mmarathe/Documents/GitHub/my_CATS/CATS-CaliforniaTestSystem/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64AEAD93-EB22-764B-BE37-49D5EABED810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2283A2DF-4EDC-E542-B952-FEC563F25A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3260" yWindow="2260" windowWidth="28040" windowHeight="17180" xr2:uid="{8EB89366-2FE9-9C44-A971-9D86756AE5B2}"/>
+    <workbookView xWindow="12540" yWindow="3340" windowWidth="28040" windowHeight="17180" activeTab="2" xr2:uid="{8EB89366-2FE9-9C44-A971-9D86756AE5B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="12">
   <si>
     <t>Shasta</t>
   </si>
@@ -66,6 +68,15 @@
   </si>
   <si>
     <t>Week of March 19 - 25, 2019</t>
+  </si>
+  <si>
+    <t>Selected generators assumed to have no cost in baseline case</t>
+  </si>
+  <si>
+    <t>All hydro generators assumed to have $1/MWh cost. In greedy case, selected generators have market offers</t>
+  </si>
+  <si>
+    <t>Note: The min and max hydro limit was taken from GODEEP</t>
   </si>
 </sst>
 </file>
@@ -437,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDDF099E-D281-6D42-A7FA-6C5C6EE7A7EC}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -518,6 +529,197 @@
         <v>8</v>
       </c>
     </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64F9C666-6E6E-5742-91F5-0C933BAACB80}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.1640625" customWidth="1"/>
+    <col min="6" max="6" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>850939</v>
+      </c>
+      <c r="C2">
+        <v>919334</v>
+      </c>
+      <c r="E2">
+        <f>100*(C2-B2)/B2</f>
+        <v>8.037591413720607</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>220833</v>
+      </c>
+      <c r="C3">
+        <v>239263</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E4" si="0">100*(C3-B3)/B3</f>
+        <v>8.345672974600717</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>13400</v>
+      </c>
+      <c r="C4">
+        <v>15675</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>16.977611940298509</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5891D445-BFC7-2447-BFD3-346843CDAB27}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.1640625" customWidth="1"/>
+    <col min="6" max="6" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>850939</v>
+      </c>
+      <c r="C2">
+        <v>884737</v>
+      </c>
+      <c r="E2">
+        <f>100*(C2-B2)/B2</f>
+        <v>3.9718475707424385</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>220833</v>
+      </c>
+      <c r="C3">
+        <v>229606</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E4" si="0">100*(C3-B3)/B3</f>
+        <v>3.9726852417890441</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>13400</v>
+      </c>
+      <c r="C4">
+        <v>14338</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/greedy_baseline_comparison.xlsx
+++ b/results/greedy_baseline_comparison.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mmarathe/Documents/GitHub/my_CATS/CATS-CaliforniaTestSystem/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2283A2DF-4EDC-E542-B952-FEC563F25A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD8AEE47-809B-CC4A-AFA9-E7C9693E8EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12540" yWindow="3340" windowWidth="28040" windowHeight="17180" activeTab="2" xr2:uid="{8EB89366-2FE9-9C44-A971-9D86756AE5B2}"/>
+    <workbookView xWindow="6520" yWindow="3340" windowWidth="28040" windowHeight="17180" activeTab="2" xr2:uid="{8EB89366-2FE9-9C44-A971-9D86756AE5B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="15">
   <si>
     <t>Shasta</t>
   </si>
@@ -77,6 +77,15 @@
   </si>
   <si>
     <t>Note: The min and max hydro limit was taken from GODEEP</t>
+  </si>
+  <si>
+    <t>greedy price</t>
+  </si>
+  <si>
+    <t>baseline price</t>
+  </si>
+  <si>
+    <t>forecast price</t>
   </si>
 </sst>
 </file>
@@ -129,6 +138,3936 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Shadow</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> price ($/MWh)</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>greedy price</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$F$2:$F$169</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="168"/>
+                <c:pt idx="0">
+                  <c:v>15.245919299999899</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15.241679805</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15.245919299999899</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15.311065045333301</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15.589394208333299</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16.01415965</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15.4787118507999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14.91956592</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14.174345099999901</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13.9539855658333</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13.5200382600002</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13.747717611999899</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14.0387436999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14.355251441199901</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15.241679805</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>15.250637552000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>15.6459172073333</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>16.0141596499999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>16.049586076566602</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>15.9219910583999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>15.5021727666666</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>15.2353519566666</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>15.184250625400001</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>15.134934449099999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>14.9124002408</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>15.140227342399999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>15.454543174633301</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>15.900699544799901</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>15.9219910583999</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>15.816728202</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>15.311065045333301</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>14.3485687508</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>14.1743451</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>14.0387436999999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>14.355251441199901</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>14.287145166666599</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>14.3485687508</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>14.3485687508</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>15.4959218224999</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>15.6923518806666</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>16.01415965</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>15.672787073999899</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>15.5603536358333</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>15.250532553999999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>15.075891824333301</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>14.504041855999899</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>14.383554827099999</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>14.3344083611999</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>14.3833330896666</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>15.184250625400001</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>15.4514987898</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>15.8965385</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>15.454543174633301</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>15.173153118</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>13.0833443347</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>12.262014848266601</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>12.071253515</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>12.083415641866599</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>11.1849420449999</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>10.837893881333301</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>11.7532590646</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>12.729763984</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>14.340238255999999</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>15.569206149999999</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>15.803695267999901</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>15.569206149999999</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>15.311065045333301</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>15.173153118</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>14.3485687508</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>14.287145166666599</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>14.1743451</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>14.0387436999999</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>14.054627225000001</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>14.4387582278999</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>15.241679805</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>15.569206149999999</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>15.184250625400001</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>13.3853052083333</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>12.071253515</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>11.0826948996</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>11.0826948996</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>10.66104595</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>10.837893881333301</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>10.915626250000001</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>11.527326533999901</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>13.627435765333299</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>15.173153117999901</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>15.6923518806666</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>15.9219910583999</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>15.8674259013333</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>15.569206149999999</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>15.311065045333301</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>15.238478051</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>15.134934449099999</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>14.968106179999999</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>14.3833330896666</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>15.134934449099999</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>15.2277068309999</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>15.184250625400001</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>14.3833330896666</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>12.64993357</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>12.071253515</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>10.837893881333301</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>9.7704589266666595</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>10.1859575481999</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>13.634075558933301</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>15.173153118</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>15.394193250000001</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>15.250637552000001</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>15.238478051</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>15.134934449099999</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>14.3485687508</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>14.1743451</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>14.0387436999999</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>13.903142299999899</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>13.903142300000001</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>14.039673859999899</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>14.287145166666599</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>14.464647759999901</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>13.91136822</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>11.0826948996</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>7.3603508029999896</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>7.4480923179999996</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>10.263999079866601</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>11.5807602514999</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>14.383554827099999</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>15.8674259013333</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>16.263071579999998</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>15.926653324999901</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>15.6923518806666</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>15.4514987898</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>15.241679805</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>15.250532553999999</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>15.6239188248</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>16.325289366666599</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>15.250637552000001</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>13.903142299999899</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>12.071253515</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>11.0755680453333</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>10.915626285166599</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>11.0826948996</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>11.1849420449999</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>11.520418826899901</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>12.262014848266601</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>13.307958430799999</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>15.2394604099999</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>16.3724106837</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>16.696337162066602</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>16.386953498999901</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>15.926653324999901</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>15.627119368400001</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>15.4356603832</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CC14-3246-AC27-7F2BFCCA4152}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>forecast price</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$H$2:$H$169</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="168"/>
+                <c:pt idx="0">
+                  <c:v>16.049586076566598</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.7730632778333</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15.596671731499901</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15.569206149999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15.627173494933299</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>16.325289366666599</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>17.266154723899998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16.696337162066598</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>15.454543174633299</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14.504041855999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13.903142299999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12.818500668799899</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12.647507207199901</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>12.5014625539999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12.784186699999999</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>12.784186699999999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>14.0387436999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>15.596671731499901</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>17.168734766666599</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>17.314356759799999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>17.2834840249999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>16.775991759900002</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>16.4401250999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>15.9219910584</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>15.6481454899999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>15.502172766666598</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>15.4377794666666</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>15.4356603832</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>15.4514987898</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>15.767589566666599</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>16.430564575666597</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>15.565558256333299</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>14.054627224999999</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>12.729763984000002</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>12.262014848266599</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>11.9013907193333</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>11.8811367105</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>11.461043850000001</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>11.1849420449999</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>11.9013907193333</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>13.792039651666601</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>15.502172766666598</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>17.168734639999901</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>17.314356759799999</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>17.346722552199999</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>17.235976095200002</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>16.696337162066598</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>16.206800481299901</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>15.867425901333299</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>15.767589566666599</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>15.6923518806666</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>15.8388596264</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>16.1355185452333</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>17.108373879999998</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>17.974179700000001</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>16.325289366666599</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>14.9861514681666</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>13.676120470999999</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>12.632559670000001</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>12.2874736825</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>12.071253515</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>11.9013907193333</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>12.2874736825</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>13.3853052083333</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>14.0387436999999</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>15.816728202</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>17.7401405748999</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>18.072790083599902</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>17.974179699999901</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>17.283484025</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>16.696337162066598</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>16.325289366666599</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>15.921991058399898</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>15.896538499999899</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>15.790041004319901</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>15.727440454</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>15.900699544799899</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>16.557749107466599</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>17.289228900000001</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>16.263071579999902</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>14.968106179999999</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>13.894321281666601</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>12.3902840689</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>11.9013907193333</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>11.9013907193333</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>11.9013907193333</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>12.071253515</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>13.019719276666599</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>14.3344083611999</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>15.6698696863333</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>17.283673749599899</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>17.9674336848</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>17.617760484799902</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>17.265878099999998</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>16.7583716544666</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>16.325289366666599</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>16.020798128639999</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>15.917988129999902</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>15.867425901333299</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>15.867425901333299</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>15.900699544799899</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>16.325289366666599</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>16.527867621600002</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>15.554022210600001</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>14.0387436999999</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>12.239262776666601</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>11.0755680453333</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>10.4220933979999</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>10.4220933979999</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>10.837893881333301</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>11.3178082455</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>12.2651589528</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>13.937936675133301</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>15.596671731499901</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>17.2446109694</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>17.509087835700001</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>17.311449501599899</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>17.196867827999899</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>16.527867621600002</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>16.181127920133299</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>15.923717326999899</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>15.892075607399999</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>15.803695267999899</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>15.7730632778333</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>15.836931359999902</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>15.921067052000001</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>16.01415965</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>15.250637552000001</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>13.033550999199999</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>11.527326533999901</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>10.525919102400001</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>10.419790828966599</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>10.4220933979999</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>10.4220933979999</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>11.0755680453333</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>11.9013907193333</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>14.0387436999999</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>15.867425901333299</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>17.346722552199999</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>17.974179700000001</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>17.385321244999901</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>17.235181187999999</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>16.4669808328333</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>16.136906975999899</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>15.9219910584</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>15.892075607399999</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>15.867425901333299</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>15.859308372479999</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>15.926653324999899</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>16.696337162066598</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>17.346722552199999</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>16.181127920133299</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>15.140227342400001</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>14.0387436999999</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>13.903142299999999</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>13.561905984166598</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>12.8185006688</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>13.3853052083333</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>14.0387436999999</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>14.3485687508</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>16.557749107466599</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>18.043046077900001</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>18.096065685599999</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>18.030046135500001</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>17.289228900000001</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>16.696337162066598</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>16.325289366666599</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-CC14-3246-AC27-7F2BFCCA4152}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="852487999"/>
+        <c:axId val="852479935"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="852487999"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="852479935"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="852479935"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="852487999"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Shadow price ($/MWh)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>greedy price</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$F$2:$F$169</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="168"/>
+                <c:pt idx="0">
+                  <c:v>15.245919299999899</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15.241679805</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15.245919299999899</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15.311065045333301</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15.589394208333299</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16.01415965</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15.4787118507999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14.91956592</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14.174345099999901</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13.9539855658333</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13.5200382600002</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13.747717611999899</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14.0387436999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14.355251441199901</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15.241679805</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>15.250637552000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>15.6459172073333</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>16.0141596499999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>16.049586076566602</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>15.9219910583999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>15.5021727666666</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>15.2353519566666</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>15.184250625400001</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>15.134934449099999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>14.9124002408</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>15.140227342399999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>15.454543174633301</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>15.900699544799901</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>15.9219910583999</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>15.816728202</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>15.311065045333301</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>14.3485687508</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>14.1743451</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>14.0387436999999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>14.355251441199901</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>14.287145166666599</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>14.3485687508</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>14.3485687508</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>15.4959218224999</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>15.6923518806666</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>16.01415965</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>15.672787073999899</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>15.5603536358333</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>15.250532553999999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>15.075891824333301</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>14.504041855999899</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>14.383554827099999</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>14.3344083611999</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>14.3833330896666</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>15.184250625400001</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>15.4514987898</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>15.8965385</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>15.454543174633301</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>15.173153118</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>13.0833443347</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>12.262014848266601</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>12.071253515</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>12.083415641866599</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>11.1849420449999</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>10.837893881333301</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>11.7532590646</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>12.729763984</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>14.340238255999999</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>15.569206149999999</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>15.803695267999901</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>15.569206149999999</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>15.311065045333301</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>15.173153118</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>14.3485687508</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>14.287145166666599</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>14.1743451</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>14.0387436999999</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>14.054627225000001</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>14.4387582278999</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>15.241679805</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>15.569206149999999</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>15.184250625400001</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>13.3853052083333</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>12.071253515</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>11.0826948996</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>11.0826948996</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>10.66104595</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>10.837893881333301</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>10.915626250000001</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>11.527326533999901</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>13.627435765333299</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>15.173153117999901</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>15.6923518806666</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>15.9219910583999</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>15.8674259013333</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>15.569206149999999</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>15.311065045333301</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>15.238478051</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>15.134934449099999</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>14.968106179999999</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>14.3833330896666</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>15.134934449099999</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>15.2277068309999</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>15.184250625400001</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>14.3833330896666</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>12.64993357</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>12.071253515</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>10.837893881333301</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>9.7704589266666595</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>10.1859575481999</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>13.634075558933301</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>15.173153118</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>15.394193250000001</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>15.250637552000001</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>15.238478051</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>15.134934449099999</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>14.3485687508</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>14.1743451</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>14.0387436999999</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>13.903142299999899</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>13.903142300000001</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>14.039673859999899</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>14.287145166666599</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>14.464647759999901</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>13.91136822</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>11.0826948996</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>7.3603508029999896</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>7.4480923179999996</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>10.263999079866601</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>11.5807602514999</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>14.383554827099999</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>15.8674259013333</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>16.263071579999998</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>15.926653324999901</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>15.6923518806666</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>15.4514987898</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>15.241679805</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>15.250532553999999</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>15.6239188248</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>16.325289366666599</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>15.250637552000001</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>13.903142299999899</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>12.071253515</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>11.0755680453333</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>10.915626285166599</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>11.0826948996</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>11.1849420449999</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>11.520418826899901</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>12.262014848266601</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>13.307958430799999</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>15.2394604099999</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>16.3724106837</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>16.696337162066602</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>16.386953498999901</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>15.926653324999901</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>15.627119368400001</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>15.4356603832</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-70D7-E545-9670-5852859460E2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>baseline price</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$G$2:$G$169</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="168"/>
+                <c:pt idx="0">
+                  <c:v>15.250532553999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.2394604099999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15.2394604099999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15.311065045333301</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15.6239188248</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16.183977229333301</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15.5021727666666</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14.621634086666599</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14.039673859999899</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13.903142300000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13.036185419999899</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13.5840670039999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14.0387436999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14.3402382559999</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>15.245919299999899</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>15.596671731499899</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>16.206800481299901</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>16.263071579999998</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>15.9726763943333</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>15.5397001059999</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>15.24125828</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>15.2277068309999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>14.968106179999999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>14.621634086666599</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>14.990640275000001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>15.481086426999999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>15.9179881299999</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>15.900699544799901</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>15.6923518806666</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>15.2505325539999</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>14.3344083611999</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>14.054627225000001</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>14.0387436999999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>14.340238255999999</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>14.1743451</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>14.3344083611999</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>14.340238255999999</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>15.455332535799901</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>15.803695267999901</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>16.1355185452333</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>15.6923518806666</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>15.569206149999999</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>15.250637552000001</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>15.140227342399999</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>14.621634086666599</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>14.504041855999899</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>14.340238255999999</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>14.504041855999899</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>15.227706831000001</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>15.4738450716</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>15.908353089999901</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>15.4828128093333</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>15.1436461125333</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>12.813434207199901</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>12.2392627766666</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>11.9013907193333</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>11.9013907193333</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>11.0826948996</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>10.633569928299901</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>11.527326533999901</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>12.632559669999999</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>14.355251441199901</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>15.596671731499899</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>15.8674259013333</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>15.596671731499899</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>15.342730428333301</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>15.184250625400001</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>14.355251441199901</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>14.3344083611999</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>14.1743451</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>14.0387436999999</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>14.174345099999901</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>14.621634086666599</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>15.2505325539999</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>15.596671731499899</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>15.2352938833333</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>13.036185419999899</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>11.9013907193333</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>10.9938227906666</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>10.9938227906666</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>10.479001149999901</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>10.5865981028</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>10.837893881333301</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>11.4610438499999</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>13.3079584307999</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>15.184250625400001</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>15.73270366</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>15.9726763943333</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>15.900699544799901</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>15.596671731499899</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>15.3657304559999</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>15.1436461125333</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>15.075891824333301</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>14.438758227899999</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>15.1436461125333</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>15.238478051</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>15.2353519566666</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>14.3545886166666</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>12.632559669999999</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>11.9013907193333</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>10.5616259450666</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>7.3691249545000099</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>10.0902931382</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>13.320560580999899</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>15.2277068309999</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>15.437512099999999</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>15.311065045333301</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>15.238478051</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>15.140227342399999</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>14.355251441199901</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>14.287145166666599</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>14.0387436999999</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>13.903142300000001</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>13.903142300000001</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>14.1743451</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>14.3344083611999</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>14.621634086666599</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>13.903142299999899</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>10.8987516173333</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>7.0275286100000001</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>10.1760171393333</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>11.520418826899901</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>14.504041855999899</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>15.900699544799901</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>16.325289366666599</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>16.01415965</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>15.73270366</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>15.4738450716</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>15.2505325539999</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>15.2394604099999</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>15.2384780509999</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>15.273590202599999</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>15.662719981</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>16.325289366666599</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>15.311065045333301</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>13.8276982768</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>11.9013907193333</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>10.837893881333301</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>10.837893881333301</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>10.9938227906666</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>11.0826948996</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>11.3178082455</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>12.2392627766666</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>12.971564362499899</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>15.245919299999899</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>16.4401250999999</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>16.696337162066602</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>16.485382124966598</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>16.01415965</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>15.6638314041</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>15.4377794666666</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-70D7-E545-9670-5852859460E2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="997025407"/>
+        <c:axId val="997027199"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="997025407"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="997027199"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="997027199"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="997025407"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>110067</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>135466</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>33866</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EE27019-A9F9-5AB8-3D18-F00DD534397E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>787400</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>194733</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1634067</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>93133</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3900E3EA-0272-A115-DD4A-D0277A5AD7A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -634,28 +4573,37 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5891D445-BFC7-2447-BFD3-346843CDAB27}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" customWidth="1"/>
     <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.1640625" customWidth="1"/>
-    <col min="6" max="6" width="34" customWidth="1"/>
+    <col min="4" max="4" width="24.83203125" customWidth="1"/>
+    <col min="5" max="5" width="2.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>4</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -665,12 +4613,21 @@
       <c r="C2">
         <v>884737</v>
       </c>
-      <c r="E2">
+      <c r="D2">
         <f>100*(C2-B2)/B2</f>
         <v>3.9718475707424385</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2">
+        <v>15.245919299999899</v>
+      </c>
+      <c r="G2">
+        <v>15.250532553999999</v>
+      </c>
+      <c r="H2">
+        <v>16.049586076566598</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -680,12 +4637,21 @@
       <c r="C3">
         <v>229606</v>
       </c>
-      <c r="E3">
-        <f t="shared" ref="E3:E4" si="0">100*(C3-B3)/B3</f>
+      <c r="D3">
+        <f t="shared" ref="D3:D4" si="0">100*(C3-B3)/B3</f>
         <v>3.9726852417890441</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3">
+        <v>15.2384780509999</v>
+      </c>
+      <c r="G3">
+        <v>15.2394604099999</v>
+      </c>
+      <c r="H3">
+        <v>15.7730632778333</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -695,33 +4661,1850 @@
       <c r="C4">
         <v>14338</v>
       </c>
-      <c r="E4">
+      <c r="D4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F4">
+        <v>15.241679805</v>
+      </c>
+      <c r="G4">
+        <v>15.2384780509999</v>
+      </c>
+      <c r="H4">
+        <v>15.596671731499901</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F5">
+        <v>15.245919299999899</v>
+      </c>
+      <c r="G5">
+        <v>15.2394604099999</v>
+      </c>
+      <c r="H5">
+        <v>15.569206149999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F6">
+        <v>15.311065045333301</v>
+      </c>
+      <c r="G6">
+        <v>15.311065045333301</v>
+      </c>
+      <c r="H6">
+        <v>15.627173494933299</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F7">
+        <v>15.589394208333299</v>
+      </c>
+      <c r="G7">
+        <v>15.6239188248</v>
+      </c>
+      <c r="H7">
+        <v>16.325289366666599</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F8">
+        <v>16.01415965</v>
+      </c>
+      <c r="G8">
+        <v>16.183977229333301</v>
+      </c>
+      <c r="H8">
+        <v>17.266154723899998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>10</v>
       </c>
+      <c r="F9">
+        <v>15.4787118507999</v>
+      </c>
+      <c r="G9">
+        <v>15.5021727666666</v>
+      </c>
+      <c r="H9">
+        <v>16.696337162066598</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F10">
+        <v>14.91956592</v>
+      </c>
+      <c r="G10">
+        <v>14.621634086666599</v>
+      </c>
+      <c r="H10">
+        <v>15.454543174633299</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F11">
+        <v>14.174345099999901</v>
+      </c>
+      <c r="G11">
+        <v>14.039673859999899</v>
+      </c>
+      <c r="H11">
+        <v>14.504041855999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F12">
+        <v>13.9539855658333</v>
+      </c>
+      <c r="G12">
+        <v>13.903142300000001</v>
+      </c>
+      <c r="H12">
+        <v>13.903142299999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F13">
+        <v>13.5200382600002</v>
+      </c>
+      <c r="G13">
+        <v>13.036185419999899</v>
+      </c>
+      <c r="H13">
+        <v>12.818500668799899</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F14">
+        <v>13.747717611999899</v>
+      </c>
+      <c r="G14">
+        <v>13.5840670039999</v>
+      </c>
+      <c r="H14">
+        <v>12.647507207199901</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F15">
+        <v>14.0387436999999</v>
+      </c>
+      <c r="G15">
+        <v>14.0387436999999</v>
+      </c>
+      <c r="H15">
+        <v>12.5014625539999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F16">
+        <v>14.355251441199901</v>
+      </c>
+      <c r="G16">
+        <v>14.3402382559999</v>
+      </c>
+      <c r="H16">
+        <v>12.784186699999999</v>
+      </c>
+    </row>
+    <row r="17" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F17">
+        <v>15.241679805</v>
+      </c>
+      <c r="G17">
+        <v>15.2384780509999</v>
+      </c>
+      <c r="H17">
+        <v>12.784186699999999</v>
+      </c>
+    </row>
+    <row r="18" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F18">
+        <v>15.250637552000001</v>
+      </c>
+      <c r="G18">
+        <v>15.245919299999899</v>
+      </c>
+      <c r="H18">
+        <v>14.0387436999999</v>
+      </c>
+    </row>
+    <row r="19" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F19">
+        <v>15.6459172073333</v>
+      </c>
+      <c r="G19">
+        <v>15.596671731499899</v>
+      </c>
+      <c r="H19">
+        <v>15.596671731499901</v>
+      </c>
+    </row>
+    <row r="20" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F20">
+        <v>16.0141596499999</v>
+      </c>
+      <c r="G20">
+        <v>16.206800481299901</v>
+      </c>
+      <c r="H20">
+        <v>17.168734766666599</v>
+      </c>
+    </row>
+    <row r="21" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F21">
+        <v>16.049586076566602</v>
+      </c>
+      <c r="G21">
+        <v>16.263071579999998</v>
+      </c>
+      <c r="H21">
+        <v>17.314356759799999</v>
+      </c>
+    </row>
+    <row r="22" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F22">
+        <v>15.9219910583999</v>
+      </c>
+      <c r="G22">
+        <v>15.9726763943333</v>
+      </c>
+      <c r="H22">
+        <v>17.2834840249999</v>
+      </c>
+    </row>
+    <row r="23" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F23">
+        <v>15.5021727666666</v>
+      </c>
+      <c r="G23">
+        <v>15.5397001059999</v>
+      </c>
+      <c r="H23">
+        <v>16.775991759900002</v>
+      </c>
+    </row>
+    <row r="24" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F24">
+        <v>15.2384780509999</v>
+      </c>
+      <c r="G24">
+        <v>15.24125828</v>
+      </c>
+      <c r="H24">
+        <v>16.4401250999999</v>
+      </c>
+    </row>
+    <row r="25" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F25">
+        <v>15.2353519566666</v>
+      </c>
+      <c r="G25">
+        <v>15.2384780509999</v>
+      </c>
+      <c r="H25">
+        <v>15.9219910584</v>
+      </c>
+    </row>
+    <row r="26" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F26">
+        <v>15.184250625400001</v>
+      </c>
+      <c r="G26">
+        <v>15.2277068309999</v>
+      </c>
+      <c r="H26">
+        <v>15.6481454899999</v>
+      </c>
+    </row>
+    <row r="27" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F27">
+        <v>15.134934449099999</v>
+      </c>
+      <c r="G27">
+        <v>14.968106179999999</v>
+      </c>
+      <c r="H27">
+        <v>15.502172766666598</v>
+      </c>
+    </row>
+    <row r="28" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F28">
+        <v>14.9124002408</v>
+      </c>
+      <c r="G28">
+        <v>14.621634086666599</v>
+      </c>
+      <c r="H28">
+        <v>15.4377794666666</v>
+      </c>
+    </row>
+    <row r="29" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F29">
+        <v>15.140227342399999</v>
+      </c>
+      <c r="G29">
+        <v>14.990640275000001</v>
+      </c>
+      <c r="H29">
+        <v>15.4356603832</v>
+      </c>
+    </row>
+    <row r="30" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F30">
+        <v>15.2384780509999</v>
+      </c>
+      <c r="G30">
+        <v>15.2384780509999</v>
+      </c>
+      <c r="H30">
+        <v>15.4514987898</v>
+      </c>
+    </row>
+    <row r="31" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F31">
+        <v>15.454543174633301</v>
+      </c>
+      <c r="G31">
+        <v>15.481086426999999</v>
+      </c>
+      <c r="H31">
+        <v>15.767589566666599</v>
+      </c>
+    </row>
+    <row r="32" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F32">
+        <v>15.900699544799901</v>
+      </c>
+      <c r="G32">
+        <v>15.9179881299999</v>
+      </c>
+      <c r="H32">
+        <v>16.430564575666597</v>
+      </c>
+    </row>
+    <row r="33" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F33">
+        <v>15.9219910583999</v>
+      </c>
+      <c r="G33">
+        <v>15.900699544799901</v>
+      </c>
+      <c r="H33">
+        <v>15.565558256333299</v>
+      </c>
+    </row>
+    <row r="34" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F34">
+        <v>15.816728202</v>
+      </c>
+      <c r="G34">
+        <v>15.6923518806666</v>
+      </c>
+      <c r="H34">
+        <v>14.054627224999999</v>
+      </c>
+    </row>
+    <row r="35" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F35">
+        <v>15.311065045333301</v>
+      </c>
+      <c r="G35">
+        <v>15.2505325539999</v>
+      </c>
+      <c r="H35">
+        <v>12.729763984000002</v>
+      </c>
+    </row>
+    <row r="36" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F36">
+        <v>14.3485687508</v>
+      </c>
+      <c r="G36">
+        <v>14.3344083611999</v>
+      </c>
+      <c r="H36">
+        <v>12.262014848266599</v>
+      </c>
+    </row>
+    <row r="37" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F37">
+        <v>14.1743451</v>
+      </c>
+      <c r="G37">
+        <v>14.054627225000001</v>
+      </c>
+      <c r="H37">
+        <v>11.9013907193333</v>
+      </c>
+    </row>
+    <row r="38" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F38">
+        <v>14.0387436999999</v>
+      </c>
+      <c r="G38">
+        <v>14.0387436999999</v>
+      </c>
+      <c r="H38">
+        <v>11.8811367105</v>
+      </c>
+    </row>
+    <row r="39" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F39">
+        <v>14.355251441199901</v>
+      </c>
+      <c r="G39">
+        <v>14.340238255999999</v>
+      </c>
+      <c r="H39">
+        <v>11.461043850000001</v>
+      </c>
+    </row>
+    <row r="40" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F40">
+        <v>14.287145166666599</v>
+      </c>
+      <c r="G40">
+        <v>14.1743451</v>
+      </c>
+      <c r="H40">
+        <v>11.1849420449999</v>
+      </c>
+    </row>
+    <row r="41" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F41">
+        <v>14.3485687508</v>
+      </c>
+      <c r="G41">
+        <v>14.3344083611999</v>
+      </c>
+      <c r="H41">
+        <v>11.9013907193333</v>
+      </c>
+    </row>
+    <row r="42" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F42">
+        <v>14.3485687508</v>
+      </c>
+      <c r="G42">
+        <v>14.340238255999999</v>
+      </c>
+      <c r="H42">
+        <v>13.792039651666601</v>
+      </c>
+    </row>
+    <row r="43" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F43">
+        <v>15.4959218224999</v>
+      </c>
+      <c r="G43">
+        <v>15.455332535799901</v>
+      </c>
+      <c r="H43">
+        <v>15.502172766666598</v>
+      </c>
+    </row>
+    <row r="44" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F44">
+        <v>15.6923518806666</v>
+      </c>
+      <c r="G44">
+        <v>15.803695267999901</v>
+      </c>
+      <c r="H44">
+        <v>17.168734639999901</v>
+      </c>
+    </row>
+    <row r="45" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F45">
+        <v>16.01415965</v>
+      </c>
+      <c r="G45">
+        <v>16.1355185452333</v>
+      </c>
+      <c r="H45">
+        <v>17.314356759799999</v>
+      </c>
+    </row>
+    <row r="46" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F46">
+        <v>15.672787073999899</v>
+      </c>
+      <c r="G46">
+        <v>15.6923518806666</v>
+      </c>
+      <c r="H46">
+        <v>17.346722552199999</v>
+      </c>
+    </row>
+    <row r="47" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F47">
+        <v>15.5603536358333</v>
+      </c>
+      <c r="G47">
+        <v>15.569206149999999</v>
+      </c>
+      <c r="H47">
+        <v>17.235976095200002</v>
+      </c>
+    </row>
+    <row r="48" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F48">
+        <v>15.250532553999999</v>
+      </c>
+      <c r="G48">
+        <v>15.250637552000001</v>
+      </c>
+      <c r="H48">
+        <v>16.696337162066598</v>
+      </c>
+    </row>
+    <row r="49" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F49">
+        <v>15.075891824333301</v>
+      </c>
+      <c r="G49">
+        <v>15.140227342399999</v>
+      </c>
+      <c r="H49">
+        <v>16.206800481299901</v>
+      </c>
+    </row>
+    <row r="50" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F50">
+        <v>14.504041855999899</v>
+      </c>
+      <c r="G50">
+        <v>14.621634086666599</v>
+      </c>
+      <c r="H50">
+        <v>15.867425901333299</v>
+      </c>
+    </row>
+    <row r="51" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F51">
+        <v>14.383554827099999</v>
+      </c>
+      <c r="G51">
+        <v>14.504041855999899</v>
+      </c>
+      <c r="H51">
+        <v>15.767589566666599</v>
+      </c>
+    </row>
+    <row r="52" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F52">
+        <v>14.3344083611999</v>
+      </c>
+      <c r="G52">
+        <v>14.340238255999999</v>
+      </c>
+      <c r="H52">
+        <v>15.6923518806666</v>
+      </c>
+    </row>
+    <row r="53" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F53">
+        <v>14.3833330896666</v>
+      </c>
+      <c r="G53">
+        <v>14.504041855999899</v>
+      </c>
+      <c r="H53">
+        <v>15.8388596264</v>
+      </c>
+    </row>
+    <row r="54" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F54">
+        <v>15.184250625400001</v>
+      </c>
+      <c r="G54">
+        <v>15.227706831000001</v>
+      </c>
+      <c r="H54">
+        <v>16.1355185452333</v>
+      </c>
+    </row>
+    <row r="55" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F55">
+        <v>15.4514987898</v>
+      </c>
+      <c r="G55">
+        <v>15.4738450716</v>
+      </c>
+      <c r="H55">
+        <v>17.108373879999998</v>
+      </c>
+    </row>
+    <row r="56" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F56">
+        <v>15.8965385</v>
+      </c>
+      <c r="G56">
+        <v>15.908353089999901</v>
+      </c>
+      <c r="H56">
+        <v>17.974179700000001</v>
+      </c>
+    </row>
+    <row r="57" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F57">
+        <v>15.454543174633301</v>
+      </c>
+      <c r="G57">
+        <v>15.4828128093333</v>
+      </c>
+      <c r="H57">
+        <v>16.325289366666599</v>
+      </c>
+    </row>
+    <row r="58" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F58">
+        <v>15.173153118</v>
+      </c>
+      <c r="G58">
+        <v>15.1436461125333</v>
+      </c>
+      <c r="H58">
+        <v>14.9861514681666</v>
+      </c>
+    </row>
+    <row r="59" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F59">
+        <v>13.0833443347</v>
+      </c>
+      <c r="G59">
+        <v>12.813434207199901</v>
+      </c>
+      <c r="H59">
+        <v>13.676120470999999</v>
+      </c>
+    </row>
+    <row r="60" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F60">
+        <v>12.262014848266601</v>
+      </c>
+      <c r="G60">
+        <v>12.2392627766666</v>
+      </c>
+      <c r="H60">
+        <v>12.632559670000001</v>
+      </c>
+    </row>
+    <row r="61" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F61">
+        <v>12.071253515</v>
+      </c>
+      <c r="G61">
+        <v>11.9013907193333</v>
+      </c>
+      <c r="H61">
+        <v>12.2874736825</v>
+      </c>
+    </row>
+    <row r="62" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F62">
+        <v>12.083415641866599</v>
+      </c>
+      <c r="G62">
+        <v>11.9013907193333</v>
+      </c>
+      <c r="H62">
+        <v>12.071253515</v>
+      </c>
+    </row>
+    <row r="63" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F63">
+        <v>11.1849420449999</v>
+      </c>
+      <c r="G63">
+        <v>11.0826948996</v>
+      </c>
+      <c r="H63">
+        <v>11.9013907193333</v>
+      </c>
+    </row>
+    <row r="64" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F64">
+        <v>10.837893881333301</v>
+      </c>
+      <c r="G64">
+        <v>10.633569928299901</v>
+      </c>
+      <c r="H64">
+        <v>12.2874736825</v>
+      </c>
+    </row>
+    <row r="65" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F65">
+        <v>11.7532590646</v>
+      </c>
+      <c r="G65">
+        <v>11.527326533999901</v>
+      </c>
+      <c r="H65">
+        <v>13.3853052083333</v>
+      </c>
+    </row>
+    <row r="66" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F66">
+        <v>12.729763984</v>
+      </c>
+      <c r="G66">
+        <v>12.632559669999999</v>
+      </c>
+      <c r="H66">
+        <v>14.0387436999999</v>
+      </c>
+    </row>
+    <row r="67" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F67">
+        <v>14.340238255999999</v>
+      </c>
+      <c r="G67">
+        <v>14.355251441199901</v>
+      </c>
+      <c r="H67">
+        <v>15.816728202</v>
+      </c>
+    </row>
+    <row r="68" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F68">
+        <v>15.569206149999999</v>
+      </c>
+      <c r="G68">
+        <v>15.596671731499899</v>
+      </c>
+      <c r="H68">
+        <v>17.7401405748999</v>
+      </c>
+    </row>
+    <row r="69" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F69">
+        <v>15.803695267999901</v>
+      </c>
+      <c r="G69">
+        <v>15.8674259013333</v>
+      </c>
+      <c r="H69">
+        <v>18.072790083599902</v>
+      </c>
+    </row>
+    <row r="70" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F70">
+        <v>15.569206149999999</v>
+      </c>
+      <c r="G70">
+        <v>15.596671731499899</v>
+      </c>
+      <c r="H70">
+        <v>17.974179699999901</v>
+      </c>
+    </row>
+    <row r="71" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F71">
+        <v>15.311065045333301</v>
+      </c>
+      <c r="G71">
+        <v>15.342730428333301</v>
+      </c>
+      <c r="H71">
+        <v>17.283484025</v>
+      </c>
+    </row>
+    <row r="72" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F72">
+        <v>15.173153118</v>
+      </c>
+      <c r="G72">
+        <v>15.184250625400001</v>
+      </c>
+      <c r="H72">
+        <v>16.696337162066598</v>
+      </c>
+    </row>
+    <row r="73" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F73">
+        <v>14.3485687508</v>
+      </c>
+      <c r="G73">
+        <v>14.355251441199901</v>
+      </c>
+      <c r="H73">
+        <v>16.325289366666599</v>
+      </c>
+    </row>
+    <row r="74" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F74">
+        <v>14.287145166666599</v>
+      </c>
+      <c r="G74">
+        <v>14.3344083611999</v>
+      </c>
+      <c r="H74">
+        <v>15.921991058399898</v>
+      </c>
+    </row>
+    <row r="75" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F75">
+        <v>14.1743451</v>
+      </c>
+      <c r="G75">
+        <v>14.1743451</v>
+      </c>
+      <c r="H75">
+        <v>15.896538499999899</v>
+      </c>
+    </row>
+    <row r="76" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F76">
+        <v>14.0387436999999</v>
+      </c>
+      <c r="G76">
+        <v>14.0387436999999</v>
+      </c>
+      <c r="H76">
+        <v>15.790041004319901</v>
+      </c>
+    </row>
+    <row r="77" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F77">
+        <v>14.054627225000001</v>
+      </c>
+      <c r="G77">
+        <v>14.174345099999901</v>
+      </c>
+      <c r="H77">
+        <v>15.727440454</v>
+      </c>
+    </row>
+    <row r="78" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F78">
+        <v>14.4387582278999</v>
+      </c>
+      <c r="G78">
+        <v>14.621634086666599</v>
+      </c>
+      <c r="H78">
+        <v>15.900699544799899</v>
+      </c>
+    </row>
+    <row r="79" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F79">
+        <v>15.241679805</v>
+      </c>
+      <c r="G79">
+        <v>15.2505325539999</v>
+      </c>
+      <c r="H79">
+        <v>16.557749107466599</v>
+      </c>
+    </row>
+    <row r="80" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F80">
+        <v>15.569206149999999</v>
+      </c>
+      <c r="G80">
+        <v>15.596671731499899</v>
+      </c>
+      <c r="H80">
+        <v>17.289228900000001</v>
+      </c>
+    </row>
+    <row r="81" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F81">
+        <v>15.184250625400001</v>
+      </c>
+      <c r="G81">
+        <v>15.2352938833333</v>
+      </c>
+      <c r="H81">
+        <v>16.263071579999902</v>
+      </c>
+    </row>
+    <row r="82" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F82">
+        <v>13.3853052083333</v>
+      </c>
+      <c r="G82">
+        <v>13.036185419999899</v>
+      </c>
+      <c r="H82">
+        <v>14.968106179999999</v>
+      </c>
+    </row>
+    <row r="83" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F83">
+        <v>12.071253515</v>
+      </c>
+      <c r="G83">
+        <v>11.9013907193333</v>
+      </c>
+      <c r="H83">
+        <v>13.894321281666601</v>
+      </c>
+    </row>
+    <row r="84" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F84">
+        <v>11.0826948996</v>
+      </c>
+      <c r="G84">
+        <v>10.9938227906666</v>
+      </c>
+      <c r="H84">
+        <v>12.3902840689</v>
+      </c>
+    </row>
+    <row r="85" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F85">
+        <v>11.0826948996</v>
+      </c>
+      <c r="G85">
+        <v>10.9938227906666</v>
+      </c>
+      <c r="H85">
+        <v>11.9013907193333</v>
+      </c>
+    </row>
+    <row r="86" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F86">
+        <v>10.66104595</v>
+      </c>
+      <c r="G86">
+        <v>10.479001149999901</v>
+      </c>
+      <c r="H86">
+        <v>11.9013907193333</v>
+      </c>
+    </row>
+    <row r="87" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F87">
+        <v>10.837893881333301</v>
+      </c>
+      <c r="G87">
+        <v>10.5865981028</v>
+      </c>
+      <c r="H87">
+        <v>11.9013907193333</v>
+      </c>
+    </row>
+    <row r="88" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F88">
+        <v>10.915626250000001</v>
+      </c>
+      <c r="G88">
+        <v>10.837893881333301</v>
+      </c>
+      <c r="H88">
+        <v>12.071253515</v>
+      </c>
+    </row>
+    <row r="89" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F89">
+        <v>11.527326533999901</v>
+      </c>
+      <c r="G89">
+        <v>11.4610438499999</v>
+      </c>
+      <c r="H89">
+        <v>13.019719276666599</v>
+      </c>
+    </row>
+    <row r="90" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F90">
+        <v>13.627435765333299</v>
+      </c>
+      <c r="G90">
+        <v>13.3079584307999</v>
+      </c>
+      <c r="H90">
+        <v>14.3344083611999</v>
+      </c>
+    </row>
+    <row r="91" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F91">
+        <v>15.173153117999901</v>
+      </c>
+      <c r="G91">
+        <v>15.184250625400001</v>
+      </c>
+      <c r="H91">
+        <v>15.6698696863333</v>
+      </c>
+    </row>
+    <row r="92" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F92">
+        <v>15.6923518806666</v>
+      </c>
+      <c r="G92">
+        <v>15.73270366</v>
+      </c>
+      <c r="H92">
+        <v>17.283673749599899</v>
+      </c>
+    </row>
+    <row r="93" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F93">
+        <v>15.9219910583999</v>
+      </c>
+      <c r="G93">
+        <v>15.9726763943333</v>
+      </c>
+      <c r="H93">
+        <v>17.9674336848</v>
+      </c>
+    </row>
+    <row r="94" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F94">
+        <v>15.8674259013333</v>
+      </c>
+      <c r="G94">
+        <v>15.900699544799901</v>
+      </c>
+      <c r="H94">
+        <v>17.617760484799902</v>
+      </c>
+    </row>
+    <row r="95" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F95">
+        <v>15.569206149999999</v>
+      </c>
+      <c r="G95">
+        <v>15.596671731499899</v>
+      </c>
+      <c r="H95">
+        <v>17.265878099999998</v>
+      </c>
+    </row>
+    <row r="96" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F96">
+        <v>15.311065045333301</v>
+      </c>
+      <c r="G96">
+        <v>15.3657304559999</v>
+      </c>
+      <c r="H96">
+        <v>16.7583716544666</v>
+      </c>
+    </row>
+    <row r="97" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F97">
+        <v>15.238478051</v>
+      </c>
+      <c r="G97">
+        <v>15.2384780509999</v>
+      </c>
+      <c r="H97">
+        <v>16.325289366666599</v>
+      </c>
+    </row>
+    <row r="98" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F98">
+        <v>15.134934449099999</v>
+      </c>
+      <c r="G98">
+        <v>15.1436461125333</v>
+      </c>
+      <c r="H98">
+        <v>16.020798128639999</v>
+      </c>
+    </row>
+    <row r="99" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F99">
+        <v>14.968106179999999</v>
+      </c>
+      <c r="G99">
+        <v>15.075891824333301</v>
+      </c>
+      <c r="H99">
+        <v>15.917988129999902</v>
+      </c>
+    </row>
+    <row r="100" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F100">
+        <v>14.3833330896666</v>
+      </c>
+      <c r="G100">
+        <v>14.438758227899999</v>
+      </c>
+      <c r="H100">
+        <v>15.867425901333299</v>
+      </c>
+    </row>
+    <row r="101" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F101">
+        <v>15.134934449099999</v>
+      </c>
+      <c r="G101">
+        <v>15.1436461125333</v>
+      </c>
+      <c r="H101">
+        <v>15.867425901333299</v>
+      </c>
+    </row>
+    <row r="102" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F102">
+        <v>15.2277068309999</v>
+      </c>
+      <c r="G102">
+        <v>15.238478051</v>
+      </c>
+      <c r="H102">
+        <v>15.900699544799899</v>
+      </c>
+    </row>
+    <row r="103" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F103">
+        <v>15.184250625400001</v>
+      </c>
+      <c r="G103">
+        <v>15.2353519566666</v>
+      </c>
+      <c r="H103">
+        <v>16.325289366666599</v>
+      </c>
+    </row>
+    <row r="104" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F104">
+        <v>15.2384780509999</v>
+      </c>
+      <c r="G104">
+        <v>15.2384780509999</v>
+      </c>
+      <c r="H104">
+        <v>16.527867621600002</v>
+      </c>
+    </row>
+    <row r="105" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F105">
+        <v>14.3833330896666</v>
+      </c>
+      <c r="G105">
+        <v>14.3545886166666</v>
+      </c>
+      <c r="H105">
+        <v>15.554022210600001</v>
+      </c>
+    </row>
+    <row r="106" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F106">
+        <v>12.64993357</v>
+      </c>
+      <c r="G106">
+        <v>12.632559669999999</v>
+      </c>
+      <c r="H106">
+        <v>14.0387436999999</v>
+      </c>
+    </row>
+    <row r="107" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F107">
+        <v>12.071253515</v>
+      </c>
+      <c r="G107">
+        <v>11.9013907193333</v>
+      </c>
+      <c r="H107">
+        <v>12.239262776666601</v>
+      </c>
+    </row>
+    <row r="108" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F108">
+        <v>10.837893881333301</v>
+      </c>
+      <c r="G108">
+        <v>10.5616259450666</v>
+      </c>
+      <c r="H108">
+        <v>11.0755680453333</v>
+      </c>
+    </row>
+    <row r="109" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F109">
+        <v>9.7704589266666595</v>
+      </c>
+      <c r="G109">
+        <v>7.3691249545000099</v>
+      </c>
+      <c r="H109">
+        <v>10.4220933979999</v>
+      </c>
+    </row>
+    <row r="110" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F110">
+        <v>7.0275286100000001</v>
+      </c>
+      <c r="G110">
+        <v>7.0275286100000001</v>
+      </c>
+      <c r="H110">
+        <v>10.4220933979999</v>
+      </c>
+    </row>
+    <row r="111" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F111">
+        <v>7.0275286100000001</v>
+      </c>
+      <c r="G111">
+        <v>7.0275286100000001</v>
+      </c>
+      <c r="H111">
+        <v>10.837893881333301</v>
+      </c>
+    </row>
+    <row r="112" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F112">
+        <v>7.0275286100000001</v>
+      </c>
+      <c r="G112">
+        <v>7.0275286100000001</v>
+      </c>
+      <c r="H112">
+        <v>11.3178082455</v>
+      </c>
+    </row>
+    <row r="113" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F113">
+        <v>7.0275286100000001</v>
+      </c>
+      <c r="G113">
+        <v>7.0275286100000001</v>
+      </c>
+      <c r="H113">
+        <v>12.2651589528</v>
+      </c>
+    </row>
+    <row r="114" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F114">
+        <v>10.1859575481999</v>
+      </c>
+      <c r="G114">
+        <v>10.0902931382</v>
+      </c>
+      <c r="H114">
+        <v>13.937936675133301</v>
+      </c>
+    </row>
+    <row r="115" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F115">
+        <v>13.634075558933301</v>
+      </c>
+      <c r="G115">
+        <v>13.320560580999899</v>
+      </c>
+      <c r="H115">
+        <v>15.596671731499901</v>
+      </c>
+    </row>
+    <row r="116" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F116">
+        <v>15.173153118</v>
+      </c>
+      <c r="G116">
+        <v>15.2277068309999</v>
+      </c>
+      <c r="H116">
+        <v>17.2446109694</v>
+      </c>
+    </row>
+    <row r="117" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F117">
+        <v>15.394193250000001</v>
+      </c>
+      <c r="G117">
+        <v>15.437512099999999</v>
+      </c>
+      <c r="H117">
+        <v>17.509087835700001</v>
+      </c>
+    </row>
+    <row r="118" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F118">
+        <v>15.250637552000001</v>
+      </c>
+      <c r="G118">
+        <v>15.311065045333301</v>
+      </c>
+      <c r="H118">
+        <v>17.311449501599899</v>
+      </c>
+    </row>
+    <row r="119" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F119">
+        <v>15.238478051</v>
+      </c>
+      <c r="G119">
+        <v>15.238478051</v>
+      </c>
+      <c r="H119">
+        <v>17.196867827999899</v>
+      </c>
+    </row>
+    <row r="120" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F120">
+        <v>15.134934449099999</v>
+      </c>
+      <c r="G120">
+        <v>15.140227342399999</v>
+      </c>
+      <c r="H120">
+        <v>16.527867621600002</v>
+      </c>
+    </row>
+    <row r="121" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F121">
+        <v>14.3485687508</v>
+      </c>
+      <c r="G121">
+        <v>14.355251441199901</v>
+      </c>
+      <c r="H121">
+        <v>16.181127920133299</v>
+      </c>
+    </row>
+    <row r="122" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F122">
+        <v>14.1743451</v>
+      </c>
+      <c r="G122">
+        <v>14.287145166666599</v>
+      </c>
+      <c r="H122">
+        <v>15.923717326999899</v>
+      </c>
+    </row>
+    <row r="123" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F123">
+        <v>14.0387436999999</v>
+      </c>
+      <c r="G123">
+        <v>14.0387436999999</v>
+      </c>
+      <c r="H123">
+        <v>15.892075607399999</v>
+      </c>
+    </row>
+    <row r="124" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F124">
+        <v>13.903142299999899</v>
+      </c>
+      <c r="G124">
+        <v>13.903142300000001</v>
+      </c>
+      <c r="H124">
+        <v>15.803695267999899</v>
+      </c>
+    </row>
+    <row r="125" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F125">
+        <v>13.903142300000001</v>
+      </c>
+      <c r="G125">
+        <v>13.903142300000001</v>
+      </c>
+      <c r="H125">
+        <v>15.7730632778333</v>
+      </c>
+    </row>
+    <row r="126" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F126">
+        <v>14.039673859999899</v>
+      </c>
+      <c r="G126">
+        <v>14.1743451</v>
+      </c>
+      <c r="H126">
+        <v>15.836931359999902</v>
+      </c>
+    </row>
+    <row r="127" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F127">
+        <v>14.287145166666599</v>
+      </c>
+      <c r="G127">
+        <v>14.3344083611999</v>
+      </c>
+      <c r="H127">
+        <v>15.921067052000001</v>
+      </c>
+    </row>
+    <row r="128" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F128">
+        <v>14.464647759999901</v>
+      </c>
+      <c r="G128">
+        <v>14.621634086666599</v>
+      </c>
+      <c r="H128">
+        <v>16.01415965</v>
+      </c>
+    </row>
+    <row r="129" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F129">
+        <v>13.91136822</v>
+      </c>
+      <c r="G129">
+        <v>13.903142299999899</v>
+      </c>
+      <c r="H129">
+        <v>15.250637552000001</v>
+      </c>
+    </row>
+    <row r="130" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F130">
+        <v>11.0826948996</v>
+      </c>
+      <c r="G130">
+        <v>10.8987516173333</v>
+      </c>
+      <c r="H130">
+        <v>13.033550999199999</v>
+      </c>
+    </row>
+    <row r="131" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F131">
+        <v>7.3603508029999896</v>
+      </c>
+      <c r="G131">
+        <v>7.0275286100000001</v>
+      </c>
+      <c r="H131">
+        <v>11.527326533999901</v>
+      </c>
+    </row>
+    <row r="132" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F132">
+        <v>7.0275286100000001</v>
+      </c>
+      <c r="G132">
+        <v>7.0275286100000001</v>
+      </c>
+      <c r="H132">
+        <v>10.525919102400001</v>
+      </c>
+    </row>
+    <row r="133" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F133">
+        <v>7.0275286100000001</v>
+      </c>
+      <c r="G133">
+        <v>7.0275286100000001</v>
+      </c>
+      <c r="H133">
+        <v>10.419790828966599</v>
+      </c>
+    </row>
+    <row r="134" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F134">
+        <v>7.0275286100000001</v>
+      </c>
+      <c r="G134">
+        <v>7.0275286100000001</v>
+      </c>
+      <c r="H134">
+        <v>10.4220933979999</v>
+      </c>
+    </row>
+    <row r="135" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F135">
+        <v>7.0275286100000001</v>
+      </c>
+      <c r="G135">
+        <v>7.0275286100000001</v>
+      </c>
+      <c r="H135">
+        <v>10.4220933979999</v>
+      </c>
+    </row>
+    <row r="136" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F136">
+        <v>7.4480923179999996</v>
+      </c>
+      <c r="G136">
+        <v>7.0275286100000001</v>
+      </c>
+      <c r="H136">
+        <v>11.0755680453333</v>
+      </c>
+    </row>
+    <row r="137" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F137">
+        <v>10.263999079866601</v>
+      </c>
+      <c r="G137">
+        <v>10.1760171393333</v>
+      </c>
+      <c r="H137">
+        <v>11.9013907193333</v>
+      </c>
+    </row>
+    <row r="138" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F138">
+        <v>11.5807602514999</v>
+      </c>
+      <c r="G138">
+        <v>11.520418826899901</v>
+      </c>
+      <c r="H138">
+        <v>14.0387436999999</v>
+      </c>
+    </row>
+    <row r="139" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F139">
+        <v>14.383554827099999</v>
+      </c>
+      <c r="G139">
+        <v>14.504041855999899</v>
+      </c>
+      <c r="H139">
+        <v>15.867425901333299</v>
+      </c>
+    </row>
+    <row r="140" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F140">
+        <v>15.8674259013333</v>
+      </c>
+      <c r="G140">
+        <v>15.900699544799901</v>
+      </c>
+      <c r="H140">
+        <v>17.346722552199999</v>
+      </c>
+    </row>
+    <row r="141" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F141">
+        <v>16.263071579999998</v>
+      </c>
+      <c r="G141">
+        <v>16.325289366666599</v>
+      </c>
+      <c r="H141">
+        <v>17.974179700000001</v>
+      </c>
+    </row>
+    <row r="142" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F142">
+        <v>15.926653324999901</v>
+      </c>
+      <c r="G142">
+        <v>16.01415965</v>
+      </c>
+      <c r="H142">
+        <v>17.385321244999901</v>
+      </c>
+    </row>
+    <row r="143" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F143">
+        <v>15.6923518806666</v>
+      </c>
+      <c r="G143">
+        <v>15.73270366</v>
+      </c>
+      <c r="H143">
+        <v>17.235181187999999</v>
+      </c>
+    </row>
+    <row r="144" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F144">
+        <v>15.4514987898</v>
+      </c>
+      <c r="G144">
+        <v>15.4738450716</v>
+      </c>
+      <c r="H144">
+        <v>16.4669808328333</v>
+      </c>
+    </row>
+    <row r="145" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F145">
+        <v>15.241679805</v>
+      </c>
+      <c r="G145">
+        <v>15.2505325539999</v>
+      </c>
+      <c r="H145">
+        <v>16.136906975999899</v>
+      </c>
+    </row>
+    <row r="146" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F146">
+        <v>15.2384780509999</v>
+      </c>
+      <c r="G146">
+        <v>15.2394604099999</v>
+      </c>
+      <c r="H146">
+        <v>15.9219910584</v>
+      </c>
+    </row>
+    <row r="147" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F147">
+        <v>15.2384780509999</v>
+      </c>
+      <c r="G147">
+        <v>15.2384780509999</v>
+      </c>
+      <c r="H147">
+        <v>15.892075607399999</v>
+      </c>
+    </row>
+    <row r="148" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F148">
+        <v>15.2384780509999</v>
+      </c>
+      <c r="G148">
+        <v>15.2384780509999</v>
+      </c>
+      <c r="H148">
+        <v>15.867425901333299</v>
+      </c>
+    </row>
+    <row r="149" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F149">
+        <v>15.2384780509999</v>
+      </c>
+      <c r="G149">
+        <v>15.2384780509999</v>
+      </c>
+      <c r="H149">
+        <v>15.859308372479999</v>
+      </c>
+    </row>
+    <row r="150" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F150">
+        <v>15.250532553999999</v>
+      </c>
+      <c r="G150">
+        <v>15.273590202599999</v>
+      </c>
+      <c r="H150">
+        <v>15.926653324999899</v>
+      </c>
+    </row>
+    <row r="151" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F151">
+        <v>15.6239188248</v>
+      </c>
+      <c r="G151">
+        <v>15.662719981</v>
+      </c>
+      <c r="H151">
+        <v>16.696337162066598</v>
+      </c>
+    </row>
+    <row r="152" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F152">
+        <v>16.325289366666599</v>
+      </c>
+      <c r="G152">
+        <v>16.325289366666599</v>
+      </c>
+      <c r="H152">
+        <v>17.346722552199999</v>
+      </c>
+    </row>
+    <row r="153" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F153">
+        <v>15.250637552000001</v>
+      </c>
+      <c r="G153">
+        <v>15.311065045333301</v>
+      </c>
+      <c r="H153">
+        <v>16.181127920133299</v>
+      </c>
+    </row>
+    <row r="154" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F154">
+        <v>13.903142299999899</v>
+      </c>
+      <c r="G154">
+        <v>13.8276982768</v>
+      </c>
+      <c r="H154">
+        <v>15.140227342400001</v>
+      </c>
+    </row>
+    <row r="155" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F155">
+        <v>12.071253515</v>
+      </c>
+      <c r="G155">
+        <v>11.9013907193333</v>
+      </c>
+      <c r="H155">
+        <v>14.0387436999999</v>
+      </c>
+    </row>
+    <row r="156" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F156">
+        <v>11.0755680453333</v>
+      </c>
+      <c r="G156">
+        <v>10.837893881333301</v>
+      </c>
+      <c r="H156">
+        <v>13.903142299999999</v>
+      </c>
+    </row>
+    <row r="157" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F157">
+        <v>10.915626285166599</v>
+      </c>
+      <c r="G157">
+        <v>10.837893881333301</v>
+      </c>
+      <c r="H157">
+        <v>13.561905984166598</v>
+      </c>
+    </row>
+    <row r="158" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F158">
+        <v>11.0826948996</v>
+      </c>
+      <c r="G158">
+        <v>10.9938227906666</v>
+      </c>
+      <c r="H158">
+        <v>12.8185006688</v>
+      </c>
+    </row>
+    <row r="159" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F159">
+        <v>11.1849420449999</v>
+      </c>
+      <c r="G159">
+        <v>11.0826948996</v>
+      </c>
+      <c r="H159">
+        <v>13.3853052083333</v>
+      </c>
+    </row>
+    <row r="160" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F160">
+        <v>11.520418826899901</v>
+      </c>
+      <c r="G160">
+        <v>11.3178082455</v>
+      </c>
+      <c r="H160">
+        <v>14.0387436999999</v>
+      </c>
+    </row>
+    <row r="161" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F161">
+        <v>12.262014848266601</v>
+      </c>
+      <c r="G161">
+        <v>12.2392627766666</v>
+      </c>
+      <c r="H161">
+        <v>14.3485687508</v>
+      </c>
+    </row>
+    <row r="162" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F162">
+        <v>13.307958430799999</v>
+      </c>
+      <c r="G162">
+        <v>12.971564362499899</v>
+      </c>
+      <c r="H162">
+        <v>15.2384780509999</v>
+      </c>
+    </row>
+    <row r="163" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F163">
+        <v>15.2394604099999</v>
+      </c>
+      <c r="G163">
+        <v>15.245919299999899</v>
+      </c>
+      <c r="H163">
+        <v>16.557749107466599</v>
+      </c>
+    </row>
+    <row r="164" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F164">
+        <v>16.3724106837</v>
+      </c>
+      <c r="G164">
+        <v>16.4401250999999</v>
+      </c>
+      <c r="H164">
+        <v>18.043046077900001</v>
+      </c>
+    </row>
+    <row r="165" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F165">
+        <v>16.696337162066602</v>
+      </c>
+      <c r="G165">
+        <v>16.696337162066602</v>
+      </c>
+      <c r="H165">
+        <v>18.096065685599999</v>
+      </c>
+    </row>
+    <row r="166" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F166">
+        <v>16.386953498999901</v>
+      </c>
+      <c r="G166">
+        <v>16.485382124966598</v>
+      </c>
+      <c r="H166">
+        <v>18.030046135500001</v>
+      </c>
+    </row>
+    <row r="167" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F167">
+        <v>15.926653324999901</v>
+      </c>
+      <c r="G167">
+        <v>16.01415965</v>
+      </c>
+      <c r="H167">
+        <v>17.289228900000001</v>
+      </c>
+    </row>
+    <row r="168" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F168">
+        <v>15.627119368400001</v>
+      </c>
+      <c r="G168">
+        <v>15.6638314041</v>
+      </c>
+      <c r="H168">
+        <v>16.696337162066598</v>
+      </c>
+    </row>
+    <row r="169" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F169">
+        <v>15.4356603832</v>
+      </c>
+      <c r="G169">
+        <v>15.4377794666666</v>
+      </c>
+      <c r="H169">
+        <v>16.325289366666599</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
